--- a/Score_ClassWork_2026.xlsx
+++ b/Score_ClassWork_2026.xlsx
@@ -1053,9 +1053,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1081,6 +1078,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1482,7 +1482,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:W56"/>
+  <dimension ref="B2:T56"/>
   <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
@@ -1493,56 +1493,56 @@
     <col min="7" max="8" width="10" hidden="1" customWidth="1"/>
     <col min="9" max="11" width="0" hidden="1" customWidth="1"/>
     <col min="12" max="13" width="4.6484375" customWidth="1"/>
-    <col min="14" max="14" width="4.6484375" style="9" customWidth="1"/>
+    <col min="14" max="14" width="4.6484375" style="8" customWidth="1"/>
     <col min="15" max="19" width="4.6484375" customWidth="1"/>
     <col min="20" max="21" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:20" ht="40" customHeight="1">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
     </row>
     <row r="3" spans="2:20" ht="23.4" customHeight="1">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
     </row>
     <row r="4" spans="2:20" ht="18">
       <c r="B4" s="1" t="s">
@@ -1580,21 +1580,21 @@
       <c r="G6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="11" t="s">
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="10" t="s">
         <v>303</v>
       </c>
     </row>
@@ -1626,20 +1626,20 @@
       <c r="J7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14">
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13">
         <v>10</v>
       </c>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="16">
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="15">
         <f>SUM(L7:S7)</f>
         <v>10</v>
       </c>
@@ -1672,20 +1672,20 @@
       <c r="J8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="13">
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="12">
         <v>8</v>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="16">
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="15">
         <f t="shared" ref="T8:T53" si="0">SUM(L8:S8)</f>
         <v>8</v>
       </c>
@@ -1718,18 +1718,18 @@
       <c r="J9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="16">
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1762,18 +1762,18 @@
       <c r="J10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="16">
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1806,20 +1806,20 @@
       <c r="J11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="13">
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="12">
         <v>7</v>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="16">
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1852,20 +1852,20 @@
       <c r="J12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="13">
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="12">
         <v>7</v>
       </c>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="16">
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1898,18 +1898,18 @@
       <c r="J13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="16">
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1942,18 +1942,18 @@
       <c r="J14" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="16">
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1986,20 +1986,20 @@
       <c r="J15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="13">
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="12">
         <v>8</v>
       </c>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="16">
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="15">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2032,20 +2032,20 @@
       <c r="J16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="13">
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="12">
         <v>10</v>
       </c>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="16">
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2078,20 +2078,20 @@
       <c r="J17" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="13">
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="12">
         <v>8</v>
       </c>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="16">
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="15">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2124,18 +2124,18 @@
       <c r="J18" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="16">
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2168,18 +2168,18 @@
       <c r="J19" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="K19" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="16">
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2212,20 +2212,20 @@
       <c r="J20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="K20" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="13">
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="12">
         <v>9</v>
       </c>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="16">
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="15">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -2258,18 +2258,18 @@
       <c r="J21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="K21" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="16">
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2302,20 +2302,20 @@
       <c r="J22" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="K22" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="13">
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="12">
         <v>7</v>
       </c>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="16">
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2348,20 +2348,20 @@
       <c r="J23" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="K23" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="13">
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="12">
         <v>10</v>
       </c>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="16">
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2394,20 +2394,20 @@
       <c r="J24" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="K24" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="13">
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="12">
         <v>7</v>
       </c>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="16">
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2440,20 +2440,20 @@
       <c r="J25" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="K25" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="13">
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="12">
         <v>7</v>
       </c>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="16">
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2486,20 +2486,20 @@
       <c r="J26" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="K26" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="13">
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="12">
         <v>10</v>
       </c>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="16">
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2532,18 +2532,18 @@
       <c r="J27" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="K27" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="16">
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2576,20 +2576,20 @@
       <c r="J28" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="K28" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="13">
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="12">
         <v>7</v>
       </c>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="16">
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2622,20 +2622,20 @@
       <c r="J29" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="K29" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="13">
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="12">
         <v>10</v>
       </c>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="16">
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2668,20 +2668,20 @@
       <c r="J30" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="K30" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="13">
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="12">
         <v>10</v>
       </c>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="16">
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2714,18 +2714,18 @@
       <c r="J31" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="K31" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="16">
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2758,20 +2758,20 @@
       <c r="J32" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="K32" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="13">
-        <v>25</v>
-      </c>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="16">
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="12">
+        <v>25</v>
+      </c>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="15">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -2804,18 +2804,18 @@
       <c r="J33" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="16">
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2848,18 +2848,18 @@
       <c r="J34" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="K34" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="16">
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2892,20 +2892,20 @@
       <c r="J35" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="K35" s="8" t="s">
+      <c r="K35" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="13">
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="12">
         <v>10</v>
       </c>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="16">
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2938,20 +2938,20 @@
       <c r="J36" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="K36" s="8" t="s">
+      <c r="K36" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="13">
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="12">
         <v>7</v>
       </c>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10"/>
-      <c r="T36" s="16">
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2984,20 +2984,20 @@
       <c r="J37" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="K37" s="8" t="s">
+      <c r="K37" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="13">
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="12">
         <v>10</v>
       </c>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="10"/>
-      <c r="S37" s="10"/>
-      <c r="T37" s="16">
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3030,20 +3030,20 @@
       <c r="J38" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="K38" s="8" t="s">
+      <c r="K38" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="13">
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="12">
         <v>10</v>
       </c>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="16">
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3076,20 +3076,20 @@
       <c r="J39" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="K39" s="8" t="s">
+      <c r="K39" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="13">
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="12">
         <v>10</v>
       </c>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="16">
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3122,20 +3122,20 @@
       <c r="J40" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="K40" s="8" t="s">
+      <c r="K40" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="13">
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="12">
         <v>9</v>
       </c>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="16">
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="15">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -3168,20 +3168,20 @@
       <c r="J41" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="K41" s="8" t="s">
+      <c r="K41" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="13">
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="12">
         <v>10</v>
       </c>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="16">
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3214,20 +3214,20 @@
       <c r="J42" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="K42" s="8" t="s">
+      <c r="K42" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="13">
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="12">
         <v>7</v>
       </c>
-      <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
-      <c r="R42" s="10"/>
-      <c r="S42" s="10"/>
-      <c r="T42" s="16">
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3260,20 +3260,20 @@
       <c r="J43" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="K43" s="8" t="s">
+      <c r="K43" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="13">
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="12">
         <v>10</v>
       </c>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="16">
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3306,20 +3306,20 @@
       <c r="J44" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K44" s="8" t="s">
+      <c r="K44" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="13">
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="12">
         <v>7</v>
       </c>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="10"/>
-      <c r="S44" s="10"/>
-      <c r="T44" s="16">
+      <c r="O44" s="9"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9"/>
+      <c r="R44" s="9"/>
+      <c r="S44" s="9"/>
+      <c r="T44" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3352,20 +3352,20 @@
       <c r="J45" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="K45" s="8" t="s">
+      <c r="K45" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="13">
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="12">
         <v>10</v>
       </c>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
-      <c r="T45" s="16">
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3398,18 +3398,18 @@
       <c r="J46" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="K46" s="8" t="s">
+      <c r="K46" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="S46" s="10"/>
-      <c r="T46" s="16">
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="9"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3442,20 +3442,20 @@
       <c r="J47" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="K47" s="8" t="s">
+      <c r="K47" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="13">
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="12">
         <v>7</v>
       </c>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="16">
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3488,20 +3488,20 @@
       <c r="J48" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="K48" s="8" t="s">
+      <c r="K48" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="13">
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="12">
         <v>7</v>
       </c>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
-      <c r="R48" s="10"/>
-      <c r="S48" s="10"/>
-      <c r="T48" s="16">
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
+      <c r="R48" s="9"/>
+      <c r="S48" s="9"/>
+      <c r="T48" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3534,20 +3534,20 @@
       <c r="J49" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="K49" s="8" t="s">
+      <c r="K49" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="13">
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="12">
         <v>10</v>
       </c>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10"/>
-      <c r="T49" s="16">
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="9"/>
+      <c r="S49" s="9"/>
+      <c r="T49" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3580,20 +3580,20 @@
       <c r="J50" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="K50" s="8" t="s">
+      <c r="K50" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="13">
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="12">
         <v>10</v>
       </c>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="10"/>
-      <c r="S50" s="10"/>
-      <c r="T50" s="16">
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="9"/>
+      <c r="R50" s="9"/>
+      <c r="S50" s="9"/>
+      <c r="T50" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3626,20 +3626,20 @@
       <c r="J51" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="K51" s="8" t="s">
+      <c r="K51" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="13">
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="12">
         <v>7</v>
       </c>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-      <c r="T51" s="16">
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="15">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3672,20 +3672,20 @@
       <c r="J52" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="K52" s="8" t="s">
+      <c r="K52" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="13">
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="12">
         <v>10</v>
       </c>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10"/>
-      <c r="T52" s="16">
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="9"/>
+      <c r="R52" s="9"/>
+      <c r="S52" s="9"/>
+      <c r="T52" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3718,20 +3718,20 @@
       <c r="J53" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="K53" s="8" t="s">
+      <c r="K53" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="13">
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="12">
         <v>10</v>
       </c>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="16">
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9"/>
+      <c r="R53" s="9"/>
+      <c r="S53" s="9"/>
+      <c r="T53" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>

--- a/Score_ClassWork_2026.xlsx
+++ b/Score_ClassWork_2026.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phisan\Consultancy\2569-KU_MapProjection\Score_KU_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5181599-4838-48B0-9479-9141D8D795B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB34E1D-B66B-4C56-8446-1432783DED8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38270" yWindow="-5990" windowWidth="23520" windowHeight="18990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="49940" yWindow="-6300" windowWidth="19420" windowHeight="18990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="303">
   <si>
     <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
   </si>
@@ -47,6 +47,9 @@
     <t>01218332-65 การฉายแผนที่ Map Projection</t>
   </si>
   <si>
+    <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
+  </si>
+  <si>
     <t>หมู่เรียน</t>
   </si>
   <si>
@@ -62,6 +65,18 @@
     <t>สรุปทั้งหมด 46 คน สถานะ Drop ติด W  0 คน</t>
   </si>
   <si>
+    <t>Ex.2 Intro to Geodesy</t>
+  </si>
+  <si>
+    <t>EX.3 Draw Sphere/Spheroid</t>
+  </si>
+  <si>
+    <t>Ex.4 EFG for Sphere</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
     <t>ลำดับที่</t>
   </si>
   <si>
@@ -110,7 +125,7 @@
     <t>E18</t>
   </si>
   <si>
-    <t/>
+    <t>25</t>
   </si>
   <si>
     <t>theerapat.ke@ku.th</t>
@@ -533,9 +548,6 @@
     <t>tanatud.m@live.ku.th</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>6710553078</t>
   </si>
   <si>
@@ -929,43 +941,35 @@
     <t>araya.sansu@live.ku.th</t>
   </si>
   <si>
-    <t>วันเวลาที่พิมพ์รายงาน 10/07/2569 00:51:06</t>
-  </si>
-  <si>
     <t>ผู้พิมพ์รายงาน ผู้ช่วยศาสตราจารย์อนุเผ่า อบแพทย์</t>
-  </si>
-  <si>
-    <t>Ex.4 EFG for Sphere</t>
-  </si>
-  <si>
-    <t>EX.3 Draw Sphere/Spheroid</t>
-  </si>
-  <si>
-    <t>Ex.2 Intro to Geodesy</t>
-  </si>
-  <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">รศ.ดร.ไพศาล สันติธรรมนนท์ </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="TH SarabunPSK"/>
-      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="TH SarabunPSK"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="6" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -974,22 +978,18 @@
       <name val="TH SarabunPSK"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="16"/>
-      <color theme="6" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="1"/>
-      <charset val="222"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1038,7 +1038,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1066,24 +1066,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1118,19 +1123,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>412750</xdr:rowOff>
+      <xdr:colOff>443230</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>62871</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>647020</xdr:colOff>
+      <xdr:colOff>1313180</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1295060</xdr:rowOff>
+      <xdr:rowOff>1420790</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ku-logo.png" descr="ku-logo.png" title="ku-logo.png">
+        <xdr:cNvPr id="2" name="/xl/media/image1.png">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -1149,8 +1154,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1054100" y="2082800"/>
-          <a:ext cx="888320" cy="882310"/>
+          <a:off x="976630" y="1028071"/>
+          <a:ext cx="1631950" cy="1586519"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1163,7 +1168,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1205,108 +1210,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1314,80 +1225,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1417,22 +1279,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -1447,43 +1309,15 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="B2:T56"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
@@ -1498,186 +1332,188 @@
     <col min="20" max="21" width="10.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" ht="40" customHeight="1">
-      <c r="B2" s="16" t="s">
+    <row r="2" spans="2:20" ht="16" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-    </row>
-    <row r="3" spans="2:20" ht="23.4" customHeight="1">
-      <c r="B3" s="16" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+    </row>
+    <row r="3" spans="2:20" ht="18.3" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="16"/>
-      <c r="S3" s="16"/>
-      <c r="T3" s="16"/>
-    </row>
-    <row r="4" spans="2:20" ht="18">
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+    </row>
+    <row r="4" spans="2:20" ht="26.1" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="17"/>
-    </row>
-    <row r="5" spans="2:20" ht="18">
+      <c r="M4" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+    </row>
+    <row r="5" spans="2:20" ht="18" x14ac:dyDescent="0.65">
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:20" ht="143.4" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" ht="120.9" customHeight="1" x14ac:dyDescent="0.65">
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
+        <v>9</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
       <c r="T6" s="10" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="7" spans="2:20" ht="20.399999999999999">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="18">
+        <v>12</v>
+      </c>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12">
         <v>10</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13">
-        <v>10</v>
-      </c>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="15">
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="13">
         <f>SUM(L7:S7)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:20" ht="20.399999999999999">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="9"/>
+        <v>32</v>
+      </c>
+      <c r="L8" s="19"/>
       <c r="M8" s="9"/>
-      <c r="N8" s="12">
+      <c r="N8" s="11">
         <v>8</v>
       </c>
       <c r="O8" s="9"/>
@@ -1685,133 +1521,135 @@
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
       <c r="S8" s="9"/>
-      <c r="T8" s="15">
+      <c r="T8" s="13">
         <f t="shared" ref="T8:T53" si="0">SUM(L8:S8)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:20" ht="20.399999999999999">
+    <row r="9" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B9" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L9" s="9"/>
+        <v>38</v>
+      </c>
+      <c r="L9" s="19"/>
       <c r="M9" s="9"/>
-      <c r="N9" s="12"/>
+      <c r="N9" s="11"/>
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
-      <c r="T9" s="15">
+      <c r="T9" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:20" ht="20.399999999999999">
+    <row r="10" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B10" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" s="9"/>
+        <v>44</v>
+      </c>
+      <c r="L10" s="19"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="12"/>
+      <c r="N10" s="11"/>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
-      <c r="T10" s="15">
+      <c r="T10" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:20" ht="20.399999999999999">
+    <row r="11" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B11" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L11" s="9"/>
+        <v>50</v>
+      </c>
+      <c r="L11" s="19">
+        <v>11</v>
+      </c>
       <c r="M11" s="9"/>
-      <c r="N11" s="12">
+      <c r="N11" s="11">
         <v>7</v>
       </c>
       <c r="O11" s="9"/>
@@ -1819,45 +1657,45 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:20" ht="20.399999999999999">
+      <c r="T11" s="13">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B12" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="9"/>
+        <v>56</v>
+      </c>
+      <c r="L12" s="19"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="12">
+      <c r="N12" s="11">
         <v>7</v>
       </c>
       <c r="O12" s="9"/>
@@ -1865,133 +1703,135 @@
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
-      <c r="T12" s="15">
+      <c r="T12" s="13">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:20" ht="20.399999999999999">
+    <row r="13" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B13" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="L13" s="9"/>
+        <v>62</v>
+      </c>
+      <c r="L13" s="19"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="12"/>
+      <c r="N13" s="11"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="15">
+      <c r="T13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:20" ht="20.399999999999999">
+    <row r="14" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B14" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L14" s="9"/>
+        <v>68</v>
+      </c>
+      <c r="L14" s="19"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="12"/>
+      <c r="N14" s="11"/>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
-      <c r="T14" s="15">
+      <c r="T14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:20" ht="20.399999999999999">
+    <row r="15" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B15" s="5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" s="9"/>
+        <v>74</v>
+      </c>
+      <c r="L15" s="19">
+        <v>12</v>
+      </c>
       <c r="M15" s="9"/>
-      <c r="N15" s="12">
+      <c r="N15" s="11">
         <v>8</v>
       </c>
       <c r="O15" s="9"/>
@@ -1999,45 +1839,45 @@
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
-      <c r="T15" s="15">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20" ht="20.399999999999999">
+      <c r="T15" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B16" s="5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="L16" s="9"/>
+        <v>80</v>
+      </c>
+      <c r="L16" s="19"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="12">
+      <c r="N16" s="11">
         <v>10</v>
       </c>
       <c r="O16" s="9"/>
@@ -2045,45 +1885,47 @@
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
-      <c r="T16" s="15">
+      <c r="T16" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:20" ht="20.399999999999999">
+    <row r="17" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B17" s="5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="L17" s="9"/>
+        <v>86</v>
+      </c>
+      <c r="L17" s="19">
+        <v>12</v>
+      </c>
       <c r="M17" s="9"/>
-      <c r="N17" s="12">
+      <c r="N17" s="11">
         <v>8</v>
       </c>
       <c r="O17" s="9"/>
@@ -2091,133 +1933,135 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="15">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" ht="20.399999999999999">
+      <c r="T17" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B18" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="L18" s="9"/>
+        <v>92</v>
+      </c>
+      <c r="L18" s="19"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="12"/>
+      <c r="N18" s="11"/>
       <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
-      <c r="T18" s="15">
+      <c r="T18" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:20" ht="20.399999999999999">
+    <row r="19" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B19" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="L19" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="L19" s="19"/>
       <c r="M19" s="9"/>
-      <c r="N19" s="12"/>
+      <c r="N19" s="11"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
-      <c r="T19" s="15">
+      <c r="T19" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:20" ht="20.399999999999999">
+    <row r="20" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B20" s="5" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="L20" s="9"/>
+        <v>104</v>
+      </c>
+      <c r="L20" s="19">
+        <v>12</v>
+      </c>
       <c r="M20" s="9"/>
-      <c r="N20" s="12">
+      <c r="N20" s="11">
         <v>9</v>
       </c>
       <c r="O20" s="9"/>
@@ -2225,89 +2069,93 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
-      <c r="T20" s="15">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" ht="20.399999999999999">
+      <c r="T20" s="13">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B21" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="L21" s="9"/>
+        <v>110</v>
+      </c>
+      <c r="L21" s="19">
+        <v>12</v>
+      </c>
       <c r="M21" s="9"/>
-      <c r="N21" s="12"/>
+      <c r="N21" s="11"/>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="9"/>
       <c r="S21" s="9"/>
-      <c r="T21" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" ht="20.399999999999999">
+      <c r="T21" s="13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B22" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="L22" s="9"/>
+        <v>116</v>
+      </c>
+      <c r="L22" s="19">
+        <v>10</v>
+      </c>
       <c r="M22" s="9"/>
-      <c r="N22" s="12">
+      <c r="N22" s="11">
         <v>7</v>
       </c>
       <c r="O22" s="9"/>
@@ -2315,45 +2163,47 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
       <c r="S22" s="9"/>
-      <c r="T22" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" ht="20.399999999999999">
+      <c r="T22" s="13">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B23" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="L23" s="9"/>
+        <v>122</v>
+      </c>
+      <c r="L23" s="19">
+        <v>8</v>
+      </c>
       <c r="M23" s="9"/>
-      <c r="N23" s="12">
+      <c r="N23" s="11">
         <v>10</v>
       </c>
       <c r="O23" s="9"/>
@@ -2361,45 +2211,47 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
-      <c r="T23" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" ht="20.399999999999999">
+      <c r="T23" s="13">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B24" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="L24" s="9"/>
+        <v>128</v>
+      </c>
+      <c r="L24" s="19">
+        <v>11</v>
+      </c>
       <c r="M24" s="9"/>
-      <c r="N24" s="12">
+      <c r="N24" s="11">
         <v>7</v>
       </c>
       <c r="O24" s="9"/>
@@ -2407,45 +2259,47 @@
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
       <c r="S24" s="9"/>
-      <c r="T24" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" ht="20.399999999999999">
+      <c r="T24" s="13">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B25" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="L25" s="9"/>
+        <v>134</v>
+      </c>
+      <c r="L25" s="19">
+        <v>6</v>
+      </c>
       <c r="M25" s="9"/>
-      <c r="N25" s="12">
+      <c r="N25" s="11">
         <v>7</v>
       </c>
       <c r="O25" s="9"/>
@@ -2453,45 +2307,47 @@
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
-      <c r="T25" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" ht="20.399999999999999">
+      <c r="T25" s="13">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B26" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="L26" s="9"/>
+        <v>140</v>
+      </c>
+      <c r="L26" s="19">
+        <v>12</v>
+      </c>
       <c r="M26" s="9"/>
-      <c r="N26" s="12">
+      <c r="N26" s="11">
         <v>10</v>
       </c>
       <c r="O26" s="9"/>
@@ -2499,89 +2355,93 @@
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
-      <c r="T26" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" ht="20.399999999999999">
+      <c r="T26" s="13">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B27" s="5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="L27" s="9"/>
+        <v>146</v>
+      </c>
+      <c r="L27" s="19">
+        <v>7</v>
+      </c>
       <c r="M27" s="9"/>
-      <c r="N27" s="12"/>
+      <c r="N27" s="11"/>
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
-      <c r="T27" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" ht="20.399999999999999">
+      <c r="T27" s="13">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B28" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="L28" s="9"/>
+        <v>152</v>
+      </c>
+      <c r="L28" s="19">
+        <v>7</v>
+      </c>
       <c r="M28" s="9"/>
-      <c r="N28" s="12">
+      <c r="N28" s="11">
         <v>7</v>
       </c>
       <c r="O28" s="9"/>
@@ -2589,45 +2449,47 @@
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
-      <c r="T28" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" ht="20.399999999999999">
+      <c r="T28" s="13">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B29" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="L29" s="9"/>
+        <v>158</v>
+      </c>
+      <c r="L29" s="19">
+        <v>6</v>
+      </c>
       <c r="M29" s="9"/>
-      <c r="N29" s="12">
+      <c r="N29" s="11">
         <v>10</v>
       </c>
       <c r="O29" s="9"/>
@@ -2635,45 +2497,47 @@
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
-      <c r="T29" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" ht="20.399999999999999">
+      <c r="T29" s="13">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B30" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="L30" s="9"/>
+        <v>164</v>
+      </c>
+      <c r="L30" s="19">
+        <v>11.5</v>
+      </c>
       <c r="M30" s="9"/>
-      <c r="N30" s="12">
+      <c r="N30" s="11">
         <v>10</v>
       </c>
       <c r="O30" s="9"/>
@@ -2681,89 +2545,91 @@
       <c r="Q30" s="9"/>
       <c r="R30" s="9"/>
       <c r="S30" s="9"/>
-      <c r="T30" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" ht="20.399999999999999">
+      <c r="T30" s="13">
+        <f t="shared" si="0"/>
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B31" s="5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="L31" s="9"/>
+        <v>170</v>
+      </c>
+      <c r="L31" s="19"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="12"/>
+      <c r="N31" s="11"/>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="15">
+      <c r="T31" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20" ht="20.399999999999999">
+    <row r="32" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B32" s="5" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="L32" s="9"/>
+        <v>175</v>
+      </c>
+      <c r="L32" s="19">
+        <v>12</v>
+      </c>
       <c r="M32" s="9"/>
-      <c r="N32" s="12">
+      <c r="N32" s="11">
         <v>25</v>
       </c>
       <c r="O32" s="9"/>
@@ -2771,133 +2637,139 @@
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
-      <c r="T32" s="15">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" ht="20.399999999999999">
+      <c r="T32" s="13">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B33" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="L33" s="9"/>
+        <v>181</v>
+      </c>
+      <c r="L33" s="19">
+        <v>5</v>
+      </c>
       <c r="M33" s="9"/>
-      <c r="N33" s="12"/>
+      <c r="N33" s="11"/>
       <c r="O33" s="9"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
-      <c r="T33" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" ht="20.399999999999999">
+      <c r="T33" s="13">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B34" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="L34" s="9"/>
+        <v>187</v>
+      </c>
+      <c r="L34" s="19">
+        <v>12</v>
+      </c>
       <c r="M34" s="9"/>
-      <c r="N34" s="12"/>
+      <c r="N34" s="11"/>
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
-      <c r="T34" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:20" ht="20.399999999999999">
+      <c r="T34" s="13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B35" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="L35" s="9"/>
+        <v>193</v>
+      </c>
+      <c r="L35" s="19">
+        <v>8</v>
+      </c>
       <c r="M35" s="9"/>
-      <c r="N35" s="12">
+      <c r="N35" s="11">
         <v>10</v>
       </c>
       <c r="O35" s="9"/>
@@ -2905,45 +2777,47 @@
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
-      <c r="T35" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="2:20" ht="20.399999999999999">
+      <c r="T35" s="13">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B36" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="L36" s="9"/>
+        <v>199</v>
+      </c>
+      <c r="L36" s="19">
+        <v>12</v>
+      </c>
       <c r="M36" s="9"/>
-      <c r="N36" s="12">
+      <c r="N36" s="11">
         <v>7</v>
       </c>
       <c r="O36" s="9"/>
@@ -2951,45 +2825,47 @@
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
-      <c r="T36" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" ht="20.399999999999999">
+      <c r="T36" s="13">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B37" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="L37" s="9"/>
+        <v>205</v>
+      </c>
+      <c r="L37" s="19">
+        <v>11</v>
+      </c>
       <c r="M37" s="9"/>
-      <c r="N37" s="12">
+      <c r="N37" s="11">
         <v>10</v>
       </c>
       <c r="O37" s="9"/>
@@ -2997,45 +2873,45 @@
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
-      <c r="T37" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="2:20" ht="20.399999999999999">
+      <c r="T37" s="13">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B38" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="L38" s="9"/>
+        <v>211</v>
+      </c>
+      <c r="L38" s="19"/>
       <c r="M38" s="9"/>
-      <c r="N38" s="12">
+      <c r="N38" s="11">
         <v>10</v>
       </c>
       <c r="O38" s="9"/>
@@ -3043,45 +2919,47 @@
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
-      <c r="T38" s="15">
+      <c r="T38" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:20" ht="20.399999999999999">
+    <row r="39" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B39" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="L39" s="9"/>
+        <v>217</v>
+      </c>
+      <c r="L39" s="19">
+        <v>12</v>
+      </c>
       <c r="M39" s="9"/>
-      <c r="N39" s="12">
+      <c r="N39" s="11">
         <v>10</v>
       </c>
       <c r="O39" s="9"/>
@@ -3089,45 +2967,47 @@
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
-      <c r="T39" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="2:20" ht="20.399999999999999">
+      <c r="T39" s="13">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B40" s="5" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K40" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="L40" s="9"/>
+        <v>223</v>
+      </c>
+      <c r="L40" s="19">
+        <v>11</v>
+      </c>
       <c r="M40" s="9"/>
-      <c r="N40" s="12">
+      <c r="N40" s="11">
         <v>9</v>
       </c>
       <c r="O40" s="9"/>
@@ -3135,45 +3015,47 @@
       <c r="Q40" s="9"/>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
-      <c r="T40" s="15">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="2:20" ht="20.399999999999999">
+      <c r="T40" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B41" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="L41" s="9"/>
+        <v>229</v>
+      </c>
+      <c r="L41" s="19">
+        <v>10</v>
+      </c>
       <c r="M41" s="9"/>
-      <c r="N41" s="12">
+      <c r="N41" s="11">
         <v>10</v>
       </c>
       <c r="O41" s="9"/>
@@ -3181,45 +3063,47 @@
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
-      <c r="T41" s="15">
-        <f t="shared" si="0"/>
+      <c r="T41" s="13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
+      <c r="B42" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="L42" s="19">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" ht="20.399999999999999">
-      <c r="B42" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="L42" s="9"/>
       <c r="M42" s="9"/>
-      <c r="N42" s="12">
+      <c r="N42" s="11">
         <v>7</v>
       </c>
       <c r="O42" s="9"/>
@@ -3227,45 +3111,47 @@
       <c r="Q42" s="9"/>
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
-      <c r="T42" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="2:20" ht="20.399999999999999">
+      <c r="T42" s="13">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B43" s="5" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="L43" s="9"/>
+        <v>241</v>
+      </c>
+      <c r="L43" s="19">
+        <v>8</v>
+      </c>
       <c r="M43" s="9"/>
-      <c r="N43" s="12">
+      <c r="N43" s="11">
         <v>10</v>
       </c>
       <c r="O43" s="9"/>
@@ -3273,45 +3159,47 @@
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
-      <c r="T43" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" ht="20.399999999999999">
+      <c r="T43" s="13">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B44" s="5" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="L44" s="9"/>
+        <v>247</v>
+      </c>
+      <c r="L44" s="19">
+        <v>5</v>
+      </c>
       <c r="M44" s="9"/>
-      <c r="N44" s="12">
+      <c r="N44" s="11">
         <v>7</v>
       </c>
       <c r="O44" s="9"/>
@@ -3319,45 +3207,47 @@
       <c r="Q44" s="9"/>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
-      <c r="T44" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="2:20" ht="20.399999999999999">
+      <c r="T44" s="13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B45" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="L45" s="9"/>
+        <v>253</v>
+      </c>
+      <c r="L45" s="19">
+        <v>8</v>
+      </c>
       <c r="M45" s="9"/>
-      <c r="N45" s="12">
+      <c r="N45" s="11">
         <v>10</v>
       </c>
       <c r="O45" s="9"/>
@@ -3365,89 +3255,93 @@
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
-      <c r="T45" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="2:20" ht="20.399999999999999">
+      <c r="T45" s="13">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B46" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="L46" s="9"/>
+        <v>259</v>
+      </c>
+      <c r="L46" s="19">
+        <v>8</v>
+      </c>
       <c r="M46" s="9"/>
-      <c r="N46" s="12"/>
+      <c r="N46" s="11"/>
       <c r="O46" s="9"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
-      <c r="T46" s="15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" ht="20.399999999999999">
+      <c r="T46" s="13">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B47" s="5" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="L47" s="9"/>
+        <v>265</v>
+      </c>
+      <c r="L47" s="19">
+        <v>10</v>
+      </c>
       <c r="M47" s="9"/>
-      <c r="N47" s="12">
+      <c r="N47" s="11">
         <v>7</v>
       </c>
       <c r="O47" s="9"/>
@@ -3455,45 +3349,47 @@
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
-      <c r="T47" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" ht="20.399999999999999">
+      <c r="T47" s="13">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B48" s="5" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="L48" s="9"/>
+        <v>271</v>
+      </c>
+      <c r="L48" s="19">
+        <v>10</v>
+      </c>
       <c r="M48" s="9"/>
-      <c r="N48" s="12">
+      <c r="N48" s="11">
         <v>7</v>
       </c>
       <c r="O48" s="9"/>
@@ -3501,45 +3397,47 @@
       <c r="Q48" s="9"/>
       <c r="R48" s="9"/>
       <c r="S48" s="9"/>
-      <c r="T48" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="2:20" ht="20.399999999999999">
+      <c r="T48" s="13">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B49" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="L49" s="9"/>
+        <v>277</v>
+      </c>
+      <c r="L49" s="19">
+        <v>11</v>
+      </c>
       <c r="M49" s="9"/>
-      <c r="N49" s="12">
+      <c r="N49" s="11">
         <v>10</v>
       </c>
       <c r="O49" s="9"/>
@@ -3547,45 +3445,47 @@
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
-      <c r="T49" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="2:20" ht="20.399999999999999">
+      <c r="T49" s="13">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B50" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="L50" s="9"/>
+        <v>283</v>
+      </c>
+      <c r="L50" s="19">
+        <v>11</v>
+      </c>
       <c r="M50" s="9"/>
-      <c r="N50" s="12">
+      <c r="N50" s="11">
         <v>10</v>
       </c>
       <c r="O50" s="9"/>
@@ -3593,45 +3493,47 @@
       <c r="Q50" s="9"/>
       <c r="R50" s="9"/>
       <c r="S50" s="9"/>
-      <c r="T50" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="2:20" ht="20.399999999999999">
+      <c r="T50" s="13">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B51" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="L51" s="9"/>
+        <v>289</v>
+      </c>
+      <c r="L51" s="19">
+        <v>7</v>
+      </c>
       <c r="M51" s="9"/>
-      <c r="N51" s="12">
+      <c r="N51" s="11">
         <v>7</v>
       </c>
       <c r="O51" s="9"/>
@@ -3639,45 +3541,47 @@
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="15">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="2:20" ht="20.399999999999999">
+      <c r="T51" s="13">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B52" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="L52" s="9"/>
+        <v>295</v>
+      </c>
+      <c r="L52" s="19">
+        <v>12</v>
+      </c>
       <c r="M52" s="9"/>
-      <c r="N52" s="12">
+      <c r="N52" s="11">
         <v>10</v>
       </c>
       <c r="O52" s="9"/>
@@ -3685,45 +3589,47 @@
       <c r="Q52" s="9"/>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
-      <c r="T52" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="2:20" ht="20.399999999999999">
+      <c r="T52" s="13">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="2:20" ht="20.399999999999999" x14ac:dyDescent="0.75">
       <c r="B53" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="L53" s="9"/>
+        <v>301</v>
+      </c>
+      <c r="L53" s="19">
+        <v>8</v>
+      </c>
       <c r="M53" s="9"/>
-      <c r="N53" s="12">
+      <c r="N53" s="11">
         <v>10</v>
       </c>
       <c r="O53" s="9"/>
@@ -3731,17 +3637,15 @@
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
-      <c r="T53" s="15">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="2:20" ht="18">
-      <c r="B56" s="1" t="s">
-        <v>298</v>
-      </c>
+      <c r="T53" s="13">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="2:20" ht="18" x14ac:dyDescent="0.65">
+      <c r="B56" s="1"/>
       <c r="G56" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -3755,8 +3659,7 @@
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="58" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>